--- a/project-management/skills/pmo-pert-estimate/examples/scenario-2-erp-migration/pert-estimate.xlsx
+++ b/project-management/skills/pmo-pert-estimate/examples/scenario-2-erp-migration/pert-estimate.xlsx
@@ -7221,233 +7221,233 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>R04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>S/4HANA cloud release breaking existing configuration</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>5, 8</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="21">
         <f>E5*F5</f>
         <v/>
       </c>
-      <c r="H5">
+      <c r="H5" s="21">
         <f>IF(G5&gt;=15,"CRITICAL",IF(G5&gt;=10,"HIGH",IF(G5&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>Subscribe to SAP release notes; enforce non-productive system upgrade testing</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="21">
         <f>L5*600</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>R05</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Integration with Port Community System delayed by third party</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>3, 5, 6</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="21">
         <f>E6*F6</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="H6" s="21">
         <f>IF(G6&gt;=15,"CRITICAL",IF(G6&gt;=10,"HIGH",IF(G6&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="21" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Maintain interface stub for testing; escalate to contract management if delayed beyond threshold</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
         <is>
           <t>PMO</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="21">
         <f>L6*600</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>R06</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>End-user resistance to new processes (change management failure)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>Organizational</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>3, 6, 7</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="21">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="H7">
+      <c r="H7" s="21">
         <f>IF(G7&gt;=15,"CRITICAL",IF(G7&gt;=10,"HIGH",IF(G7&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>Dedicated change management stream; early super-user programme; communications plan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>BDM</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="21">
         <f>L7*600</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>R07</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>ABAP custom code incompatibility with S/4HANA (deprecated APIs)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>2, 5, 6</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="21">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="H8">
+      <c r="H8" s="21">
         <f>IF(G8&gt;=15,"CRITICAL",IF(G8&gt;=10,"HIGH",IF(G8&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="21" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>SAP Readiness Check early execution; remediation budget reserved</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="21">
         <f>L8*600</f>
         <v/>
       </c>
